--- a/Stats Sheet/Round Gaps/Deviation.xlsx
+++ b/Stats Sheet/Round Gaps/Deviation.xlsx
@@ -70,6 +70,9 @@
     <x:t>18</x:t>
   </x:si>
   <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
     <x:t>_1mmortal_</x:t>
   </x:si>
   <x:si>
@@ -271,6 +274,9 @@
     <x:t>SOAKLE</x:t>
   </x:si>
   <x:si>
+    <x:t>113</x:t>
+  </x:si>
+  <x:si>
     <x:t>strategy</x:t>
   </x:si>
   <x:si>
@@ -436,6 +442,9 @@
     <x:t>Plushy33</x:t>
   </x:si>
   <x:si>
+    <x:t>236</x:t>
+  </x:si>
+  <x:si>
     <x:t>Psykl0ne</x:t>
   </x:si>
   <x:si>
@@ -586,6 +595,9 @@
     <x:t>carterwarterbear</x:t>
   </x:si>
   <x:si>
+    <x:t>285</x:t>
+  </x:si>
+  <x:si>
     <x:t>Zakkeagle</x:t>
   </x:si>
   <x:si>
@@ -713,6 +725,27 @@
   </x:si>
   <x:si>
     <x:t>Reignexion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AlolanSandshrew</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gmailol</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HellaJugDish</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUQTER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>omchris</x:t>
+  </x:si>
+  <x:si>
+    <x:t>onstep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RedDragonStar1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1071,10 +1104,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V150"/>
+  <x:dimension ref="A1:W157"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:22" s="1" customFormat="1">
+    <x:row r="1" spans="1:23" s="1" customFormat="1">
       <x:c r="E1" s="1">
         <x:v>45315</x:v>
       </x:c>
@@ -1129,8 +1162,11 @@
       <x:c r="V1" s="1">
         <x:v>46095</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:22">
+      <x:c r="W1" s="1">
+        <x:v>46130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:23">
       <x:c r="F2" s="0">
         <x:v>61</x:v>
       </x:c>
@@ -1182,8 +1218,11 @@
       <x:c r="V2" s="0">
         <x:v>16</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:22">
+      <x:c r="W2" s="0">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:23">
       <x:c r="E3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1238,140 +1277,149 @@
       <x:c r="V3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:22">
+      <x:c r="W3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:23">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:23">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="W5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:23">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>0</x:v>
@@ -1380,21 +1428,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:22">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:23">
       <x:c r="A7" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>0</x:v>
@@ -1403,15 +1451,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:23">
       <x:c r="A8" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>0</x:v>
@@ -1420,77 +1468,80 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:22">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:23">
       <x:c r="A9" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="R9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="W9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:23">
       <x:c r="A10" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>0</x:v>
@@ -1499,21 +1550,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:23">
       <x:c r="A11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>0</x:v>
@@ -1522,83 +1573,86 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:23">
       <x:c r="A12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="R12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="V12" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W12" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:23">
       <x:c r="A13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>0</x:v>
@@ -1607,54 +1661,54 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="V13" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:23">
       <x:c r="A14" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>0</x:v>
@@ -1663,160 +1717,166 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O14" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Q14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="V14" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:22">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:23">
       <x:c r="A15" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V15" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="W15" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:23">
       <x:c r="A16" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V16" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W16" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:23">
       <x:c r="A17" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>0</x:v>
@@ -1825,30 +1885,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M17" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O17" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:22">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:23">
       <x:c r="A18" s="0">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>0</x:v>
@@ -1857,33 +1917,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="P18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V18" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:22">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:23">
       <x:c r="A19" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>0</x:v>
@@ -1892,30 +1952,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O19" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q19" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="R19" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:23">
       <x:c r="A20" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>0</x:v>
@@ -1924,36 +1984,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L20" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V20" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:23">
       <x:c r="A21" s="0">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>0</x:v>
@@ -1962,86 +2022,89 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:22">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:23">
       <x:c r="A22" s="0">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V22" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W22" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:23">
       <x:c r="A23" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>0</x:v>
@@ -2050,57 +2113,57 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M23" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O23" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="P23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U23" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:23">
       <x:c r="A24" s="0">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>0</x:v>
@@ -2109,30 +2172,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P24" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="Q24" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:23">
       <x:c r="A25" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>0</x:v>
@@ -2141,24 +2204,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L25" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="R25" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S25" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:23">
       <x:c r="A26" s="0">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>0</x:v>
@@ -2167,18 +2230,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L26" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:22">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:23">
       <x:c r="A27" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>0</x:v>
@@ -2187,27 +2250,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="N27" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="O27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U27" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:22">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:23">
       <x:c r="A28" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>0</x:v>
@@ -2216,89 +2279,92 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M28" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:22">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:23">
       <x:c r="A29" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U29" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="V29" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W29" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:23">
       <x:c r="A30" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>0</x:v>
@@ -2307,51 +2373,51 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R30" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:22">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:23">
       <x:c r="A31" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>0</x:v>
@@ -2360,171 +2426,180 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M31" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="N31" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:23">
       <x:c r="A32" s="0">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L32" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="N32" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="O32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U32" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="V32" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W32" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:23">
       <x:c r="A33" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O33" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="Q33" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="U33" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="V33" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W33" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:23">
       <x:c r="A34" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q34" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="R34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S34" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W34" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:23">
       <x:c r="A35" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>0</x:v>
@@ -2533,51 +2608,51 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O35" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="P35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U35" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:22">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:23">
       <x:c r="A36" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>0</x:v>
@@ -2586,27 +2661,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L36" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:23">
       <x:c r="A37" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>0</x:v>
@@ -2615,15 +2690,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:23">
       <x:c r="A38" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>0</x:v>
@@ -2632,42 +2707,42 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M38" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="Q38" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="R38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U38" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:22">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:23">
       <x:c r="A39" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>0</x:v>
@@ -2676,27 +2751,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M39" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:22">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:23">
       <x:c r="A40" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>1</x:v>
@@ -2705,39 +2780,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N40" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="O40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R40" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V40" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:22">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:23">
       <x:c r="A41" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>1</x:v>
@@ -2746,27 +2821,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:23">
       <x:c r="A42" s="0">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>1</x:v>
@@ -2775,51 +2850,51 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S42" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="U42" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:22">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:23">
       <x:c r="A43" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>1</x:v>
@@ -2828,54 +2903,54 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M43" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q43" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="R43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V43" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:23">
       <x:c r="A44" s="0">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>1</x:v>
@@ -2884,77 +2959,80 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:23">
       <x:c r="A45" s="0">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U45" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W45" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:23">
       <x:c r="A46" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>1</x:v>
@@ -2963,33 +3041,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J46" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U46" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="V46" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:23">
       <x:c r="A47" s="0">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>1</x:v>
@@ -2998,77 +3076,80 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R47" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="V47" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:22">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:23">
       <x:c r="A48" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O48" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="P48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U48" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W48" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:23">
       <x:c r="A49" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>1</x:v>
@@ -3077,71 +3158,74 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J49" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="P49" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:22">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:23">
       <x:c r="A50" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N50" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q50" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="R50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V50" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:22">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="W50" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:23">
       <x:c r="A51" s="0">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>1</x:v>
@@ -3150,27 +3234,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="L51" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:23">
       <x:c r="A52" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>1</x:v>
@@ -3179,15 +3263,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:23">
       <x:c r="A53" s="0">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>1</x:v>
@@ -3196,15 +3280,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:23">
       <x:c r="A54" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>1</x:v>
@@ -3213,45 +3297,45 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L54" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="M54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O54" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="P54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U54" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="V54" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:23">
       <x:c r="A55" s="0">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>1</x:v>
@@ -3260,33 +3344,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="M55" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P55" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="Q55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T55" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:22">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:23">
       <x:c r="A56" s="0">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>1</x:v>
@@ -3295,36 +3379,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J56" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="Q56" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="S56" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="T56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V56" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:23">
       <x:c r="A57" s="0">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>1</x:v>
@@ -3333,104 +3417,107 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R57" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="U57" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:22">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:23">
       <x:c r="A58" s="0">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D58" s="0">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P58" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="Q58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V58" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W58" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:23">
       <x:c r="A59" s="0">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>2</x:v>
@@ -3439,18 +3526,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G59" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U59" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:22">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:23">
       <x:c r="A60" s="0">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>2</x:v>
@@ -3459,62 +3546,65 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q60" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="V60" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:22">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:23">
       <x:c r="A61" s="0">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D61" s="0">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J61" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M61" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="Q61" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="R61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V61" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="W61" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:23">
       <x:c r="A62" s="0">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>2</x:v>
@@ -3523,39 +3613,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I62" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J62" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O62" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P62" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q62" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S62" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="V62" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:22">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:23">
       <x:c r="A63" s="0">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>2</x:v>
@@ -3564,27 +3654,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I63" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L63" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N63" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:22">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:23">
       <x:c r="A64" s="0">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>2</x:v>
@@ -3593,15 +3683,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G64" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:23">
       <x:c r="A65" s="0">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>2</x:v>
@@ -3610,77 +3700,80 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J65" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N65" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="O65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T65" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="V65" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:23">
       <x:c r="A66" s="0">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D66" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H66" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I66" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M66" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="N66" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O66" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q66" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:22">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W66" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:23">
       <x:c r="A67" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>2</x:v>
@@ -3689,51 +3782,51 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R67" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="T67" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="V67" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:23">
       <x:c r="A68" s="0">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>2</x:v>
@@ -3742,48 +3835,48 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I68" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L68" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="M68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P68" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="Q68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V68" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:23">
       <x:c r="A69" s="0">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>2</x:v>
@@ -3792,39 +3885,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M69" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="N69" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O69" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P69" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q69" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R69" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T69" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="V69" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:23">
       <x:c r="A70" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>2</x:v>
@@ -3833,27 +3926,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M70" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="P70" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="Q70" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U70" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:22">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:23">
       <x:c r="A71" s="0">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>2</x:v>
@@ -3862,45 +3955,45 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O71" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="R71" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="S71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V71" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:23">
       <x:c r="A72" s="0">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>2</x:v>
@@ -3909,21 +4002,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G72" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S72" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="V72" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:22">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:23">
       <x:c r="A73" s="0">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>3</x:v>
@@ -3932,27 +4025,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H73" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q73" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="R73" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S73" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U73" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:22">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:23">
       <x:c r="A74" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>3</x:v>
@@ -3961,27 +4054,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L74" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:23">
       <x:c r="A75" s="0">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>3</x:v>
@@ -3990,18 +4083,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H75" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I75" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:23">
       <x:c r="A76" s="0">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>3</x:v>
@@ -4010,15 +4103,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H76" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:23">
       <x:c r="A77" s="0">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>3</x:v>
@@ -4027,15 +4120,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H77" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:23">
       <x:c r="A78" s="0">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>3</x:v>
@@ -4044,68 +4137,71 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H78" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J78" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L78" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M78" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O78" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="P78" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q78" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S78" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="T78" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:23">
       <x:c r="A79" s="0">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D79" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I79" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J79" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P79" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="Q79" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W79" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:23">
       <x:c r="A80" s="0">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>4</x:v>
@@ -4114,24 +4210,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I80" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q80" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="T80" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:22">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:23">
       <x:c r="A81" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>4</x:v>
@@ -4140,18 +4236,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I81" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L81" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:22">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:23">
       <x:c r="A82" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>4</x:v>
@@ -4160,21 +4256,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I82" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="U82" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:22">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:23">
       <x:c r="A83" s="0">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>4</x:v>
@@ -4183,18 +4279,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I83" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L83" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:22">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:23">
       <x:c r="A84" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>4</x:v>
@@ -4203,18 +4299,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I84" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q84" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:22">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:23">
       <x:c r="A85" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>4</x:v>
@@ -4223,36 +4319,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="I85" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J85" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L85" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="N85" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q85" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="R85" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S85" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V85" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:22">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:23">
       <x:c r="A86" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>4</x:v>
@@ -4261,56 +4357,59 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I86" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L86" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T86" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:22">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:23">
       <x:c r="A87" s="0">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D87" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J87" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O87" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q87" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="T87" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="U87" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W87" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:23">
       <x:c r="A88" s="0">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>5</x:v>
@@ -4319,68 +4418,71 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J88" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M88" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="Q88" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:22">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:23">
       <x:c r="A89" s="0">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D89" s="0">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J89" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L89" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M89" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O89" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="P89" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q89" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S89" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="T89" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V89" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="W89" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:23">
       <x:c r="A90" s="0">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>5</x:v>
@@ -4389,53 +4491,56 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J90" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P90" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="Q90" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:23">
       <x:c r="A91" s="0">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D91" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J91" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O91" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="R91" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="T91" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="U91" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V91" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W91" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:23">
       <x:c r="A92" s="0">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>5</x:v>
@@ -4444,15 +4549,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J92" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:23">
       <x:c r="A93" s="0">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>5</x:v>
@@ -4461,15 +4566,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J93" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:23">
       <x:c r="A94" s="0">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>5</x:v>
@@ -4478,33 +4583,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R94" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U94" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="V94" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:23">
       <x:c r="A95" s="0">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>6</x:v>
@@ -4513,18 +4618,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L95" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:23">
       <x:c r="A96" s="0">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>6</x:v>
@@ -4533,15 +4638,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:23">
       <x:c r="A97" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>6</x:v>
@@ -4550,15 +4655,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:23">
       <x:c r="A98" s="0">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>7</x:v>
@@ -4567,21 +4672,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="L98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S98" s="0" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:22">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:23">
       <x:c r="A99" s="0">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>7</x:v>
@@ -4590,36 +4695,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O99" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="Q99" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="R99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U99" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:23">
       <x:c r="A100" s="0">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>7</x:v>
@@ -4628,80 +4733,83 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="L100" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M100" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N100" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O100" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P100" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R100" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S100" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U100" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="V100" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:23">
       <x:c r="A101" s="0">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L101" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O101" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="P101" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q101" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R101" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S101" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T101" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U101" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V101" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W101" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:23">
       <x:c r="A102" s="0">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>8</x:v>
@@ -4710,21 +4818,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M102" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N102" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S102" s="0" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:22">
+        <x:v>187</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:23">
       <x:c r="A103" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>8</x:v>
@@ -4733,15 +4841,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M103" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:23">
       <x:c r="A104" s="0">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>8</x:v>
@@ -4750,59 +4858,62 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="M104" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q104" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="T104" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="V104" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:23">
       <x:c r="A105" s="0">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D105" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="M105" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O105" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="Q105" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="R105" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S105" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T105" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V105" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:22">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="W105" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:23">
       <x:c r="A106" s="0">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>8</x:v>
@@ -4811,35 +4922,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M106" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:23">
       <x:c r="A107" s="0">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N107" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O107" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W107" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:23">
       <x:c r="A108" s="0">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>9</x:v>
@@ -4848,21 +4962,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N108" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P108" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="S108" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:22">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:23">
       <x:c r="A109" s="0">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>10</x:v>
@@ -4871,27 +4985,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="O109" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P109" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R109" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S109" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V109" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:22">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:23">
       <x:c r="A110" s="0">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>10</x:v>
@@ -4900,24 +5014,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="O110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q110" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="S110" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="V110" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:22">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:23">
       <x:c r="A111" s="0">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>10</x:v>
@@ -4926,18 +5040,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="O111" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q111" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" spans="1:22">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:23">
       <x:c r="A112" s="0">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>10</x:v>
@@ -4946,21 +5060,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="O112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q112" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:23">
       <x:c r="A113" s="0">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>11</x:v>
@@ -4969,62 +5083,65 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="P113" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q113" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R113" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U113" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="V113" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:23">
       <x:c r="A114" s="0">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D114" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="P114" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q114" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R114" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S114" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T114" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U114" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V114" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W114" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:23">
       <x:c r="A115" s="0">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>11</x:v>
@@ -5033,18 +5150,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="P115" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q115" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:23">
       <x:c r="A116" s="0">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>11</x:v>
@@ -5053,15 +5170,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P116" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:23">
       <x:c r="A117" s="0">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>11</x:v>
@@ -5070,15 +5187,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P117" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:23">
       <x:c r="A118" s="0">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>12</x:v>
@@ -5087,15 +5204,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q118" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:23">
       <x:c r="A119" s="0">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>12</x:v>
@@ -5104,18 +5221,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q119" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T119" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" spans="1:22">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:23">
       <x:c r="A120" s="0">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>12</x:v>
@@ -5124,15 +5241,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q120" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:23">
       <x:c r="A121" s="0">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>12</x:v>
@@ -5141,24 +5258,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="Q121" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R121" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S121" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V121" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" spans="1:22">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:23">
       <x:c r="A122" s="0">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>12</x:v>
@@ -5167,15 +5284,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q122" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:23">
       <x:c r="A123" s="0">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>12</x:v>
@@ -5184,15 +5301,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q123" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:23">
       <x:c r="A124" s="0">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>13</x:v>
@@ -5201,27 +5318,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="R124" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S124" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T124" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U124" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V124" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:23">
       <x:c r="A125" s="0">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>13</x:v>
@@ -5230,15 +5347,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R125" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:23">
       <x:c r="A126" s="0">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>13</x:v>
@@ -5247,15 +5364,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R126" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:23">
       <x:c r="A127" s="0">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>13</x:v>
@@ -5264,15 +5381,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R127" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:23">
       <x:c r="A128" s="0">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>13</x:v>
@@ -5281,44 +5398,47 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R128" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:23">
       <x:c r="A129" s="0">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D129" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="R129" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="S129" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T129" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U129" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V129" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W129" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:23">
       <x:c r="A130" s="0">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>13</x:v>
@@ -5327,15 +5447,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R130" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:23">
       <x:c r="A131" s="0">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>13</x:v>
@@ -5344,15 +5464,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R131" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:23">
       <x:c r="A132" s="0">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
         <x:v>14</x:v>
@@ -5361,61 +5481,67 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S132" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:23">
       <x:c r="A133" s="0">
         <x:v>130</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D133" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="S133" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="T133" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U133" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V133" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W133" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:23">
       <x:c r="A134" s="0">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D134" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="S134" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U134" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" spans="1:22">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="W134" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:23">
       <x:c r="A135" s="0">
         <x:v>132</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>14</x:v>
@@ -5424,18 +5550,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S135" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V135" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" spans="1:22">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:23">
       <x:c r="A136" s="0">
         <x:v>133</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
         <x:v>15</x:v>
@@ -5444,15 +5570,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T136" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:23">
       <x:c r="A137" s="0">
         <x:v>134</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
         <x:v>15</x:v>
@@ -5461,21 +5587,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T137" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U137" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V137" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="138" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:23">
       <x:c r="A138" s="0">
         <x:v>135</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>15</x:v>
@@ -5484,21 +5610,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T138" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="U138" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V138" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="139" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:23">
       <x:c r="A139" s="0">
         <x:v>136</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
         <x:v>15</x:v>
@@ -5507,15 +5633,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T139" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="140" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:23">
       <x:c r="A140" s="0">
         <x:v>137</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
         <x:v>16</x:v>
@@ -5524,69 +5650,78 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U140" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="141" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:23">
       <x:c r="A141" s="0">
         <x:v>138</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D141" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="U141" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="V141" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="142" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W141" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:23">
       <x:c r="A142" s="0">
         <x:v>139</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D142" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U142" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="143" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W142" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:23">
       <x:c r="A143" s="0">
         <x:v>140</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U143" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W143" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:23">
       <x:c r="A144" s="0">
         <x:v>141</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
         <x:v>16</x:v>
@@ -5595,15 +5730,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U144" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:23">
       <x:c r="A145" s="0">
         <x:v>142</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
         <x:v>17</x:v>
@@ -5612,15 +5747,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V145" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:23">
       <x:c r="A146" s="0">
         <x:v>143</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
         <x:v>17</x:v>
@@ -5629,15 +5764,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V146" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:23">
       <x:c r="A147" s="0">
         <x:v>144</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
         <x:v>17</x:v>
@@ -5646,32 +5781,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V147" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:23">
       <x:c r="A148" s="0">
         <x:v>145</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D148" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="V148" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W148" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:23">
       <x:c r="A149" s="0">
         <x:v>146</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
         <x:v>17</x:v>
@@ -5680,24 +5818,146 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V149" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150" spans="1:22">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:23">
       <x:c r="A150" s="0">
         <x:v>147</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D150" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="V150" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="W150" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:23">
+      <x:c r="A151" s="0">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D151" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W151" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:23">
+      <x:c r="A152" s="0">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D152" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W152" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:23">
+      <x:c r="A153" s="0">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D153" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W153" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:23">
+      <x:c r="A154" s="0">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D154" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W154" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:23">
+      <x:c r="A155" s="0">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D155" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W155" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:23">
+      <x:c r="A156" s="0">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D156" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W156" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:23">
+      <x:c r="A157" s="0">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D157" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W157" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
